--- a/stories/arbres/ATOM-SEC.RUE.001-05.xlsx
+++ b/stories/arbres/ATOM-SEC.RUE.001-05.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Léonie marche avec papa. Ils vont à la boulangerie. Léonie sent le pain chaud. Ils arrivent au bord. Le bord du trottoir est là. Papa s'arrête. Léonie s'arrête aussi. S'arrêter, c'est le geste. Les pieds de Léonie sont au bord. Les pieds restent au bord. Les pieds sont sur le trottoir. Papa dit : on s'arrête. Pieds au bord. Sur le trottoir. Léonie pose les pieds au bord. Les pieds sont calmes. Papa sourit. Papa dit : bravo Léonie. On s'arrête au trottoir. On attend avec papa. Les pieds restent au bord du trottoir.</t>
+          <t>Léonie marche avec papa. Ils vont à la boulangerie. Léonie sent le pain chaud. Ils arrivent au bord. Le bord du trottoir est là. Papa s'arrête. Léonie s'arrête aussi. S'arrêter, c'est le geste. Les pieds de Léonie sont au bord. Les pieds restent au bord. Les pieds sont sur le trottoir. On s'arrête. Pieds au bord. Sur le trottoir. Léonie pose les pieds au bord. Les pieds sont calmes. Papa sourit. Bravo Léonie. On s'arrête au trottoir. On attend avec papa. Les pieds restent au bord du trottoir.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,15 @@
         <v>12</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Léonie marche avec papa. Ils vont à la boulangerie. Léonie sent le pain chaud. Ils arrivent au bord. Le bord du trottoir est là. Papa s'arrête. Léonie s'arrête aussi. S'arrêter, c'est le geste. Les pieds de Léonie sont au bord. Les pieds restent au bord. Les pieds sont sur le trottoir.
+papa|On s'arrête. Pieds au bord. Sur le trottoir.
+narrateur|Léonie pose les pieds au bord. Les pieds sont calmes. Papa sourit.
+papa|Bravo Léonie. On s'arrête au trottoir. On attend avec papa.
+narrateur|Les pieds restent au bord du trottoir.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1469,6 +1494,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Léonie arrive au bord. Que fait-elle ?</t>
         </is>
       </c>
     </row>
@@ -1641,6 +1671,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Léonie s'arrête au bord. Les pieds sont sur le trottoir. Papa est là.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1807,6 +1842,11 @@
         <v>12</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Léonie donne la main à papa. Ils attendent un moment.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1969,6 +2009,11 @@
         <v>12</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1987,7 +2032,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2004,6 +2049,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SEC.RUE.001-05.xlsx
+++ b/stories/arbres/ATOM-SEC.RUE.001-05.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1314,6 +1319,7 @@
 narrateur|Les pieds restent au bord du trottoir.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1501,6 +1507,7 @@
           <t>narrateur|Léonie arrive au bord. Que fait-elle ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1676,6 +1683,7 @@
           <t>narrateur|Léonie s'arrête au bord. Les pieds sont sur le trottoir. Papa est là.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1847,6 +1855,7 @@
           <t>narrateur|Léonie donne la main à papa. Ils attendent un moment.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2014,6 +2023,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2032,7 +2042,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2056,6 +2066,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2070,7 +2094,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2257,6 +2281,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-SEC.RUE.001-05.xlsx
+++ b/stories/arbres/ATOM-SEC.RUE.001-05.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Léonie s'arrête au trottoir</t>
+          <t>La farine de Nina</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Un nuage de farine dort sur la table. Nina et papa vont à la boulangerie. Au bord, Nina s'arrête. Pieds au bord, sur le trottoir. Le pain est tiède.</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1184,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Léonie marche avec papa. Ils vont à la boulangerie. Léonie sent le pain chaud. Ils arrivent au bord. Le bord du trottoir est là. Papa s'arrête. Léonie s'arrête aussi. S'arrêter, c'est le geste. Les pieds de Léonie sont au bord. Les pieds restent au bord. Les pieds sont sur le trottoir. On s'arrête. Pieds au bord. Sur le trottoir. Léonie pose les pieds au bord. Les pieds sont calmes. Papa sourit. Bravo Léonie. On s'arrête au trottoir. On attend avec papa. Les pieds restent au bord du trottoir.</t>
+          <t>Un nuage de farine dort sur la table. Il est blanc, tout doux sous le doigt. Une cuillère en bois sent la pâte. Le bol est encore un peu collant. Les chaussons de Nina attendent sous la chaise. Un manteau rouge pend au crochet. La cuisine sent le lait tiède. Nina vit ici, avec papa. Papa, c'est tout blanc ! Oui. C'est de la farine. On va chercher le pain ? Oui ! Tu mets tes chaussures ? En ce moment, Nina s'assoit. Elle pose les chaussons sous la chaise. Elle enfile les chaussures brunes. Tu as fini tes chaussures ? Oui, papa. Bravo. On prend le manteau rouge. Papa ouvre la porte. L'air sent le four de la rue. Ça sent le pain ! Oui. On marche sur le trottoir. Nina donne la main à papa. Le manteau rouge est un peu rêche. Une clochette sonne, tout au loin. Ding, tout doux. J'entends la clochette ! Bientôt. On reste sur le trottoir. Le bord du trottoir arrive. Le bord est gris et net. On va s'arrêter. Pieds au bord. Sur le trottoir. Nina s'arrête. Ses pieds sont au bord. Les pieds restent au bord. Les pieds sont sur le trottoir. Je m'arrête. Oui. On attend avec papa. Tes pieds sont calmes ? Oui. Le pain sent encore plus fort. Nina serre la main de papa. Bravo, Nina. Tu as fait du bon travail. Les pieds restent au bord du trottoir.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1312,10 +1324,57 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Léonie marche avec papa. Ils vont à la boulangerie. Léonie sent le pain chaud. Ils arrivent au bord. Le bord du trottoir est là. Papa s'arrête. Léonie s'arrête aussi. S'arrêter, c'est le geste. Les pieds de Léonie sont au bord. Les pieds restent au bord. Les pieds sont sur le trottoir.
-papa|On s'arrête. Pieds au bord. Sur le trottoir.
-narrateur|Léonie pose les pieds au bord. Les pieds sont calmes. Papa sourit.
-papa|Bravo Léonie. On s'arrête au trottoir. On attend avec papa.
+          <t>narrateur|Un nuage de farine dort sur la table.
+narrateur|Il est blanc, tout doux sous le doigt.
+narrateur|Une cuillère en bois sent la pâte.
+narrateur|Le bol est encore un peu collant.
+narrateur|Les chaussons de Nina attendent sous la chaise.
+narrateur|Un manteau rouge pend au crochet.
+narrateur|La cuisine sent le lait tiède.
+narrateur|Nina vit ici, avec papa.
+enfant-f|Papa, c'est tout blanc !
+papa|Oui.
+papa|C'est de la farine.
+papa|On va chercher le pain ?
+enfant-f|Oui !
+papa|Tu mets tes chaussures ?
+narrateur|En ce moment, Nina s'assoit.
+narrateur|Elle pose les chaussons sous la chaise.
+narrateur|Elle enfile les chaussures brunes.
+papa|Tu as fini tes chaussures ?
+enfant-f|Oui, papa.
+papa|Bravo.
+papa|On prend le manteau rouge.
+narrateur|Papa ouvre la porte.
+narrateur|L'air sent le four de la rue.
+enfant-f|Ça sent le pain !
+papa|Oui.
+papa|On marche sur le trottoir.
+narrateur|Nina donne la main à papa.
+narrateur|Le manteau rouge est un peu rêche.
+narrateur|Une clochette sonne, tout au loin.
+narrateur|Ding, tout doux.
+enfant-f|J'entends la clochette !
+papa|Bientôt.
+papa|On reste sur le trottoir.
+narrateur|Le bord du trottoir arrive.
+narrateur|Le bord est gris et net.
+papa|On va s'arrêter.
+papa|Pieds au bord.
+papa|Sur le trottoir.
+narrateur|Nina s'arrête.
+narrateur|Ses pieds sont au bord.
+narrateur|Les pieds restent au bord.
+narrateur|Les pieds sont sur le trottoir.
+enfant-f|Je m'arrête.
+papa|Oui.
+papa|On attend avec papa.
+papa|Tes pieds sont calmes ?
+enfant-f|Oui.
+narrateur|Le pain sent encore plus fort.
+narrateur|Nina serre la main de papa.
+papa|Bravo, Nina.
+papa|Tu as fait du bon travail.
 narrateur|Les pieds restent au bord du trottoir.</t>
         </is>
       </c>
@@ -1344,7 +1403,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Léonie arrive au bord. Que fait-elle ?</t>
+          <t>Nina arrive au bord. Que fait-elle ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1504,7 +1563,8 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Léonie arrive au bord. Que fait-elle ?</t>
+          <t>narrateur|Nina arrive au bord.
+narrateur|Que fait-elle ?</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr"/>
@@ -1532,7 +1592,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Léonie s'arrête au bord. Les pieds sont sur le trottoir. Papa est là.</t>
+          <t>Nina s'arrête au bord. Les pieds sont sur le trottoir. Les pieds restent au bord. Tu t'arrêtes au trottoir ? Oui. Je m'arrête. Bravo, Nina. On attend avec papa. La main de papa est chaude. Le manteau rouge gratte un peu. La clochette sonne encore, loin.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1680,7 +1740,17 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Léonie s'arrête au bord. Les pieds sont sur le trottoir. Papa est là.</t>
+          <t>narrateur|Nina s'arrête au bord.
+narrateur|Les pieds sont sur le trottoir.
+narrateur|Les pieds restent au bord.
+papa|Tu t'arrêtes au trottoir ?
+enfant-f|Oui.
+enfant-f|Je m'arrête.
+papa|Bravo, Nina.
+papa|On attend avec papa.
+narrateur|La main de papa est chaude.
+narrateur|Le manteau rouge gratte un peu.
+narrateur|La clochette sonne encore, loin.</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr"/>
@@ -1708,7 +1778,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Léonie donne la main à papa. Ils attendent un moment.</t>
+          <t>On y va ensemble ? Oui, papa. Ils marchent avec l'adulte. La clochette fait ding, tout près. Le pain est chaud dans le sac. Tu le touches ? Nina pose la main. Il est tiède ! Oui. Tu as fini de le toucher ? Oui. Bravo. Le sac sent le beurre. Un peu de farine reste à la maison.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1852,7 +1922,20 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Léonie donne la main à papa. Ils attendent un moment.</t>
+          <t>papa|On y va ensemble ?
+enfant-f|Oui, papa.
+narrateur|Ils marchent avec l'adulte.
+narrateur|La clochette fait ding, tout près.
+narrateur|Le pain est chaud dans le sac.
+papa|Tu le touches ?
+narrateur|Nina pose la main.
+enfant-f|Il est tiède !
+papa|Oui.
+papa|Tu as fini de le toucher ?
+enfant-f|Oui.
+papa|Bravo.
+narrateur|Le sac sent le beurre.
+narrateur|Un peu de farine reste à la maison.</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr"/>
@@ -1880,7 +1963,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Je me suis arrêtée. Pieds au bord. Sur le trottoir. Bravo, Nina. Le pain tiède reste dans le sac. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2020,7 +2103,12 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-f|Je me suis arrêtée.
+papa|Pieds au bord.
+papa|Sur le trottoir.
+papa|Bravo, Nina.
+narrateur|Le pain tiède reste dans le sac.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr"/>
@@ -2042,7 +2130,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2080,6 +2168,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SEC.RUE.001-05.xlsx
+++ b/stories/arbres/ATOM-SEC.RUE.001-05.xlsx
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Un nuage de farine dort sur la table. Il est blanc, tout doux sous le doigt. Une cuillère en bois sent la pâte. Le bol est encore un peu collant. Les chaussons de Nina attendent sous la chaise. Un manteau rouge pend au crochet. La cuisine sent le lait tiède. Nina vit ici, avec papa. Papa, c'est tout blanc ! Oui. C'est de la farine. On va chercher le pain ? Oui ! Tu mets tes chaussures ? En ce moment, Nina s'assoit. Elle pose les chaussons sous la chaise. Elle enfile les chaussures brunes. Tu as fini tes chaussures ? Oui, papa. Bravo. On prend le manteau rouge. Papa ouvre la porte. L'air sent le four de la rue. Ça sent le pain ! Oui. On marche sur le trottoir. Nina donne la main à papa. Le manteau rouge est un peu rêche. Une clochette sonne, tout au loin. Ding, tout doux. J'entends la clochette ! Bientôt. On reste sur le trottoir. Le bord du trottoir arrive. Le bord est gris et net. On va s'arrêter. Pieds au bord. Sur le trottoir. Nina s'arrête. Ses pieds sont au bord. Les pieds restent au bord. Les pieds sont sur le trottoir. Je m'arrête. Oui. On attend avec papa. Tes pieds sont calmes ? Oui. Le pain sent encore plus fort. Nina serre la main de papa. Bravo, Nina. Tu as fait du bon travail. Les pieds restent au bord du trottoir.</t>
+          <t>Un nuage de farine dort sur la table. Il est blanc, tout doux sous le doigt. Une cuillère en bois sent la pâte. Le bol est encore un peu collant. Les chaussons de Nina attendent sous la chaise. Un manteau rouge pend au crochet. La cuisine sent le lait tiède. Nina vit ici, avec papa. Papa, c'est tout blanc ! Oui. C'est de la farine. On va chercher le pain ? Oui ! Tu mets tes chaussures ? En ce moment, Nina s'assoit. Elle pose les chaussons sous la chaise. Elle enfile les chaussures brunes. Tu as fini tes chaussures ? Oui, papa. Bravo. On prend le manteau rouge. Papa ouvre la porte. L'air sent le four de la rue. Ça sent le pain ! Oui. On marche sur le trottoir. Nina donne la main à papa. Le manteau rouge est un peu rêche. Une clochette sonne, tout au loin. Ding, tout doux. J'entends la clochette ! Bientôt. On reste sur le trottoir. Le bord du trottoir arrive. Le bord est gris et net. On va s'arrêter. Pieds au bord. Sur le trottoir. Nina s'arrête. Ses pieds sont au bord. Les pieds restent au bord. Les pieds sont sur le trottoir. Je m'arrête. Oui. On attend avec papa. Tes pieds sont calmes ? Oui. Le pain sent encore plus fort. Nina serre la main de papa. Bravo, Nina. Les pieds restent au bord du trottoir.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Léonie marche avec papa. Ils vont à la boulangerie. Léonie sent le pain chaud. Ils arrivent au bord. Le bord du &lt;emphasis level="moderate"&gt;trottoir&lt;/emphasis&gt; est là. Papa s'arrête. Léonie s'arrête aussi. S'arrêter, c'est le geste. Les pieds de Léonie sont au bord. Les pieds restent au bord. Les pieds sont sur le trottoir. Papa dit : on s'arrête. Pieds au bord. Sur le trottoir. Léonie pose les pieds au bord. Les pieds sont calmes. Papa sourit. Papa dit : bravo Léonie. On s'arrête au trottoir. On attend avec papa. Les pieds restent au bord du trottoir.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>Un nuage de farine dort sur la table. Il est blanc, tout doux sous le doigt. Une cuillère en bois sent la pâte. Le bol est encore un peu collant. Les chaussons de Nina attendent sous la chaise. Un manteau rouge pend au crochet. La cuisine sent le lait tiède. Nina vit ici, avec papa. Papa, c'est tout blanc ! Oui. C'est de la farine. On va chercher le pain ? Oui ! Tu mets tes chaussures ? En ce moment, Nina s'assoit. Elle pose les chaussons sous la chaise. Elle enfile les chaussures brunes. Tu as fini tes chaussures ? Oui, papa. Bravo. On prend le manteau rouge. Papa ouvre la porte. L'air sent le four de la rue. Ça sent le pain ! Oui. On marche sur le trottoir. Nina donne la main à papa. Le manteau rouge est un peu rêche. Une clochette sonne, tout au loin. Ding, tout doux. J'entends la clochette ! Bientôt. On reste sur le trottoir. Le bord du trottoir arrive. Le bord est gris et net. On va s'arrêter. Pieds au bord. Sur le trottoir. Nina s'arrête. Ses pieds sont au bord. Les pieds restent au bord. Les pieds sont sur le trottoir. Je m'arrête. Oui. On attend avec papa. Tes pieds sont calmes ? Oui. Le pain sent encore plus fort. Nina serre la main de papa. Bravo, Nina. Les pieds restent au bord du trottoir.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1374,11 +1374,9 @@
 narrateur|Le pain sent encore plus fort.
 narrateur|Nina serre la main de papa.
 papa|Bravo, Nina.
-papa|Tu as fait du bon travail.
 narrateur|Les pieds restent au bord du trottoir.</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1408,7 +1406,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;Léonie arrive au bord. Que fait-elle ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Nina arrive au bord. Que fait-elle ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1567,7 +1565,6 @@
 narrateur|Que fait-elle ?</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1597,7 +1594,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;Léonie s'arrête au bord. Les pieds sont sur le &lt;emphasis level="moderate"&gt;trottoir&lt;/emphasis&gt;. Papa est là.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Nina s'arrête au bord. Les pieds sont sur le trottoir. Les pieds restent au bord. Tu t'arrêtes au trottoir ? Oui. Je m'arrête. Bravo, Nina. On attend avec papa. La main de papa est chaude. Le manteau rouge gratte un peu. La clochette sonne encore, loin.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1753,7 +1750,6 @@
 narrateur|La clochette sonne encore, loin.</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1783,7 +1779,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;Léonie donne la &lt;emphasis level="moderate"&gt;main&lt;/emphasis&gt; à papa. Ils attendent un moment.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>On y va ensemble ? Oui, papa. Ils marchent avec l'adulte. La clochette fait ding, tout près. Le pain est chaud dans le sac. Tu le touches ? Nina pose la main. Il est tiède ! Oui. Tu as fini de le toucher ? Oui. Bravo. Le sac sent le beurre. Un peu de farine reste à la maison.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1938,7 +1934,6 @@
 narrateur|Un peu de farine reste à la maison.</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1963,12 +1958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Je me suis arrêtée. Pieds au bord. Sur le trottoir. Bravo, Nina. Le pain tiède reste dans le sac. L'histoire est finie.</t>
+          <t>Je me suis arrêtée. Pieds au bord. Sur le trottoir. Bravo, Nina. Le pain tiède reste dans le sac.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>Je me suis arrêtée. Pieds au bord. Sur le trottoir. Bravo, Nina. Le pain tiède reste dans le sac.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2107,11 +2102,9 @@
 papa|Pieds au bord.
 papa|Sur le trottoir.
 papa|Bravo, Nina.
-narrateur|Le pain tiède reste dans le sac.
-narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+narrateur|Le pain tiède reste dans le sac.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2130,7 +2123,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2175,6 +2168,13 @@
       <c r="A6" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SEC.RUE.001-05.xlsx
+++ b/stories/arbres/ATOM-SEC.RUE.001-05.xlsx
@@ -671,7 +671,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>trajet vers la boulangerie</t>
+          <t>cuisine farinée, trottoir vers la boulangerie</t>
         </is>
       </c>
     </row>
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Léonie, papa</t>
+          <t>Nina, papa</t>
         </is>
       </c>
     </row>
